--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_134_R14.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_134_R14.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.085100000000001</v>
+        <v>9.604100000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5609</v>
+        <v>8.7103</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5241</v>
+        <v>0.8938</v>
       </c>
       <c r="G2" t="n">
         <v>7.1421</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5004</v>
+        <v>0.0187</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0351</v>
+        <v>0.1142</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4652</v>
+        <v>-0.0955</v>
       </c>
       <c r="V2" t="n">
         <v>0.8197</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3617</v>
+        <v>4.6723</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7476</v>
+        <v>5.0582</v>
       </c>
       <c r="F3" t="n">
         <v>-0.3859</v>
@@ -688,10 +688,10 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1573</v>
+        <v>0.1533</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6642</v>
+        <v>-0.3536</v>
       </c>
       <c r="U3" t="n">
         <v>0.507</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0542</v>
+        <v>2.6965</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2983</v>
+        <v>1.6716</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2441</v>
+        <v>1.0249</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.9092</v>
+        <v>-0.8367</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1719</v>
+        <v>0.8463000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.0811</v>
+        <v>-1.683</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9571</v>
+        <v>0.4105</v>
       </c>
       <c r="K4" t="n">
-        <v>0.773</v>
+        <v>1.2471</v>
       </c>
       <c r="L4" t="n">
-        <v>0.184</v>
+        <v>-0.8366</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8663</v>
+        <v>-1.2472</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6012</v>
+        <v>-0.4008</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2651</v>
+        <v>-0.8464</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>1.4273</v>
+        <v>0.3734</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1968</v>
+        <v>0.1889</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2305</v>
+        <v>0.1845</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6815</v>
+        <v>2.2213</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5222</v>
+        <v>3.7806</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1593</v>
+        <v>-1.5593</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8367</v>
+        <v>-0.1492</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8463000000000001</v>
+        <v>4.5218</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.683</v>
+        <v>-4.671</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4105</v>
+        <v>3.0316</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2471</v>
+        <v>5.2802</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.8366</v>
+        <v>-2.2486</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2472</v>
+        <v>-3.1808</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4008</v>
+        <v>-0.7584</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8464</v>
+        <v>-2.4223</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0876</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3585</v>
+        <v>0.226</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0395</v>
+        <v>-0.2357</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3189</v>
+        <v>0.4617</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7255</v>
+        <v>2.2037</v>
       </c>
       <c r="E6" t="n">
-        <v>3.352</v>
+        <v>3.0191</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6265</v>
+        <v>-0.8154</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1492</v>
+        <v>-1.9092</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5218</v>
+        <v>0.1719</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.671</v>
+        <v>-2.0811</v>
       </c>
       <c r="J6" t="n">
-        <v>3.0316</v>
+        <v>0.9571</v>
       </c>
       <c r="K6" t="n">
-        <v>5.2802</v>
+        <v>0.773</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2486</v>
+        <v>0.184</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.1808</v>
+        <v>-2.8663</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7584</v>
+        <v>-0.6012</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.4223</v>
+        <v>-2.2651</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2697</v>
+        <v>0.5768</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6642</v>
+        <v>-0.0824</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3945</v>
+        <v>0.6592</v>
       </c>
       <c r="V6" t="n">
         <v>2.1444</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3253</v>
+        <v>1.5858</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1352</v>
+        <v>2.5638</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.978</v>
       </c>
       <c r="G7" t="n">
         <v>0.7498</v>
@@ -1000,13 +1000,13 @@
         <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5996</v>
+        <v>-0.3391</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4481</v>
+        <v>-0.0196</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1516</v>
+        <v>-0.3196</v>
       </c>
       <c r="V7" t="n">
         <v>-1.6083</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2266</v>
+        <v>1.193</v>
       </c>
       <c r="E8" t="n">
         <v>0.8208</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4058</v>
+        <v>0.3722</v>
       </c>
       <c r="G8" t="n">
         <v>1.257</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2623</v>
+        <v>-0.2959</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1415</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1208</v>
+        <v>-0.1544</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.1846</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7099</v>
+        <v>0.0769</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4747</v>
+        <v>0.6091</v>
       </c>
       <c r="G9" t="n">
         <v>-0.2561</v>
@@ -1156,13 +1156,13 @@
         <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5851</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0499</v>
+        <v>0.4169</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4648</v>
+        <v>-0.3304</v>
       </c>
       <c r="V9" t="n">
         <v>-0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.2525</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.3257</v>
+        <v>-1.124</v>
       </c>
       <c r="G11" t="n">
         <v>-3.44</v>
@@ -1312,13 +1312,13 @@
         <v>1.1598</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1581</v>
+        <v>-0.112</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4955</v>
+        <v>0.0237</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3374</v>
+        <v>-0.1357</v>
       </c>
       <c r="V11" t="n">
         <v>2.6805</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>F. NTILIKINA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3688</v>
+        <v>-1.9807</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0477</v>
+        <v>-2.2484</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.3211</v>
+        <v>0.2677</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.4938</v>
+        <v>-2.0126</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0216</v>
+        <v>-0.1991</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4722</v>
+        <v>-1.8135</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3361</v>
+        <v>-1.187</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3361</v>
+        <v>0.2017</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>-1.3887</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.8299</v>
+        <v>-0.8256</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3577</v>
+        <v>-0.4008</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4722</v>
+        <v>-0.4248</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q12" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1792</v>
+        <v>-0.3598</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.224</v>
+        <v>0.0984</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0448</v>
+        <v>-0.4582</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. NTILIKINA</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.5944</v>
+        <v>-2.1837</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7948</v>
+        <v>-0.9297</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2004</v>
+        <v>-1.2539</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0126</v>
+        <v>-1.4938</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1991</v>
+        <v>-0.0216</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8135</v>
+        <v>-1.4722</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.187</v>
+        <v>0.3361</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2017</v>
+        <v>0.3361</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3887</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8256</v>
+        <v>-1.8299</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.4008</v>
+        <v>-0.3577</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4248</v>
+        <v>-1.4722</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9735</v>
+        <v>0.0059</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4481</v>
+        <v>-0.1061</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5254</v>
+        <v>0.112</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>18.712</v>
+        <v>19.4588</v>
       </c>
       <c r="E14" t="n">
-        <v>22.0287</v>
+        <v>22.7757</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.317</v>
+        <v>-3.316800000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.346700000000001</v>
@@ -1525,7 +1525,7 @@
         <v>19.7031</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3541</v>
+        <v>1.354099999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-19.7107</v>
@@ -1546,13 +1546,13 @@
         <v>19.716</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4129999999999999</v>
+        <v>0.3338000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8435000000000001</v>
+        <v>-0.09680000000000004</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4305</v>
+        <v>0.4306000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>6.180699999999999</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T. HORTON TUCKER</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.678</v>
+        <v>3.8255</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4656</v>
+        <v>5.94</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.7876</v>
+        <v>-2.1145</v>
       </c>
       <c r="G15" t="n">
-        <v>7.0651</v>
+        <v>2.0343</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7991</v>
+        <v>-2.379</v>
       </c>
       <c r="I15" t="n">
-        <v>4.266</v>
+        <v>4.4133</v>
       </c>
       <c r="J15" t="n">
-        <v>9.8247</v>
+        <v>5.0234</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7124</v>
+        <v>1.0251</v>
       </c>
       <c r="L15" t="n">
-        <v>5.1124</v>
+        <v>3.9983</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.7596</v>
+        <v>-2.9891</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.9132</v>
+        <v>-3.4041</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8464</v>
+        <v>0.415</v>
       </c>
       <c r="P15" t="n">
-        <v>-6.0307</v>
+        <v>1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>-7.1905</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5714</v>
+        <v>0.0953</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7591</v>
+        <v>-0.4597</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8123</v>
+        <v>0.5551</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>T. HORTON TUCKER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.4152</v>
+        <v>2.7858</v>
       </c>
       <c r="E16" t="n">
-        <v>5.5862</v>
+        <v>3.8758</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.171</v>
+        <v>-1.0901</v>
       </c>
       <c r="G16" t="n">
-        <v>2.0343</v>
+        <v>7.0651</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.379</v>
+        <v>2.7991</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4133</v>
+        <v>4.266</v>
       </c>
       <c r="J16" t="n">
-        <v>5.0234</v>
+        <v>9.8247</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0251</v>
+        <v>4.7124</v>
       </c>
       <c r="L16" t="n">
-        <v>3.9983</v>
+        <v>5.1124</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9891</v>
+        <v>-2.7596</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.4041</v>
+        <v>-1.9132</v>
       </c>
       <c r="O16" t="n">
-        <v>0.415</v>
+        <v>-0.8464</v>
       </c>
       <c r="P16" t="n">
+        <v>-6.0307</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-7.1905</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.1598</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3917</v>
-      </c>
       <c r="S16" t="n">
-        <v>-0.315</v>
+        <v>0.6792</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8136</v>
+        <v>0.1693</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4986</v>
+        <v>0.5098</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.773</v>
+        <v>-0.1947</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9257</v>
+        <v>1.2796</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6987</v>
+        <v>-1.4743</v>
       </c>
       <c r="G17" t="n">
         <v>3.8958</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9577</v>
+        <v>-0.3793</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0376</v>
+        <v>-0.6838</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08</v>
+        <v>0.3044</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3009</v>
+        <v>-1.8798</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3714</v>
+        <v>-0.0176</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9294</v>
+        <v>-1.8622</v>
       </c>
       <c r="G18" t="n">
         <v>-2.4154</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2618</v>
+        <v>0.1592</v>
       </c>
       <c r="T18" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.3618</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V18" t="n">
         <v>1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3268</v>
+        <v>-2.4117</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4786</v>
+        <v>-0.5590000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8481</v>
+        <v>-1.8527</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.2098</v>
+        <v>-1.1302</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4297</v>
+        <v>-2.84</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7801</v>
+        <v>1.7099</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.1982</v>
+        <v>0.7971</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7359</v>
+        <v>-0.6015</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.4623</v>
+        <v>1.3986</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0116</v>
+        <v>-1.9273</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6938</v>
+        <v>-2.2385</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.3178</v>
+        <v>0.3113</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>0.651</v>
+        <v>0.0226</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7196</v>
+        <v>0.0356</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.013</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4339</v>
+        <v>-2.4454</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3231</v>
+        <v>1.8741</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1108</v>
+        <v>-4.3195</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1302</v>
+        <v>-0.332</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.84</v>
+        <v>-1.0647</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7099</v>
+        <v>0.7327</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7971</v>
+        <v>1.8699</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6015</v>
+        <v>0.6589</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3986</v>
+        <v>1.211</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9273</v>
+        <v>-2.202</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2385</v>
+        <v>-1.7236</v>
       </c>
       <c r="O20" t="n">
-        <v>0.3113</v>
+        <v>-0.4783</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0004</v>
+        <v>0.1032</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2715</v>
+        <v>0.0042</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.271</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4955</v>
+        <v>-2.6299</v>
       </c>
       <c r="E21" t="n">
-        <v>1.992</v>
+        <v>-1.7145</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.4875</v>
+        <v>-0.9154</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.332</v>
+        <v>-3.2098</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.0647</v>
+        <v>-1.4297</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7327</v>
+        <v>-1.7801</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8699</v>
+        <v>-2.1982</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6589</v>
+        <v>-0.7359</v>
       </c>
       <c r="L21" t="n">
-        <v>1.211</v>
+        <v>-1.4623</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.202</v>
+        <v>-1.0116</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.7236</v>
+        <v>-0.6938</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4783</v>
+        <v>-0.3178</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0532</v>
+        <v>0.3479</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1221</v>
+        <v>0.4837</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.1357</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7692</v>
+        <v>-2.6677</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9491000000000001</v>
+        <v>-0.7131999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8201</v>
+        <v>-1.9545</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6972</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2838</v>
+        <v>0.3853</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4481</v>
+        <v>-0.2122</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7319</v>
+        <v>0.5975</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3558</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7284</v>
+        <v>-5.2845</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8081</v>
+        <v>-3.4543</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9203</v>
+        <v>-1.8303</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8201</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.0727</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1336</v>
+        <v>0.2203</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3831</v>
+        <v>-0.293</v>
       </c>
       <c r="V23" t="n">
         <v>-1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.9774</v>
+        <v>-7.023</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7222</v>
+        <v>-3.194</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.2551</v>
+        <v>-3.829</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7372</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0958</v>
+        <v>-0.1415</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1221</v>
+        <v>-0.3497</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2179</v>
+        <v>0.2082</v>
       </c>
       <c r="V24" t="n">
         <v>-2.6805</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-18.7119</v>
+        <v>-17.9254</v>
       </c>
       <c r="E25" t="n">
-        <v>3.317000000000001</v>
+        <v>3.3169</v>
       </c>
       <c r="F25" t="n">
-        <v>-22.0286</v>
+        <v>-21.2425</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.346700000000001</v>
+        <v>-1.346700000000002</v>
       </c>
       <c r="H25" t="n">
         <v>-14.7471</v>
@@ -2404,13 +2404,13 @@
         <v>8.118499999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4128999999999999</v>
+        <v>1.1992</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4306</v>
+        <v>-0.4304999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8435999999999999</v>
+        <v>1.6299</v>
       </c>
       <c r="V25" t="n">
         <v>-6.180699999999999</v>
